--- a/logs/Jun_15_full_log/6_15_BO1_HRP_all_res.xlsx
+++ b/logs/Jun_15_full_log/6_15_BO1_HRP_all_res.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\logs\Jun_15_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47309311-2051-4CDD-9C75-129383541843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151F2BAB-AFBA-4C5B-8B54-8DC0346D08C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,7 +417,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G385"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
